--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="269">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,8 +263,7 @@
     <t>Funktionsstatusbedömning</t>
   </si>
   <si>
-    <t>De funktionsstatusbedömningar som matchar begäran.
-Kardinalitet: Valfri, lista.</t>
+    <t>De funktionsstatusbedömningar som matchar begäran.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -356,8 +355,7 @@
     <t>Dokumenthuvud (PatientSummaryHeader)</t>
   </si>
   <si>
-    <t>Innehåller basinformation om dokumentet (PatientSummaryHeaderType).
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller basinformation om dokumentet (PatientSummaryHeaderType).</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.id</t>
@@ -372,59 +370,60 @@
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.documentId</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
+  </si>
+  <si>
     <t>Dokumentets identitet</t>
   </si>
   <si>
-    <t>Funktionsbedömningens identitet som är unik inom källsystemet.
-Kardinalitet: Obligatorisk.</t>
+    <t>Funktionsbedömningens identitet som är unik inom källsystemet.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.sourceSystemHSAId</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t>HSA-id för källsystem</t>
+  </si>
+  <si>
+    <t>HSA-id för det system som tillgängliggör informationen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.documentTitle</t>
+  </si>
+  <si>
+    <t>Titel (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetFunctionalStatus skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.documentTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
-    <t>HSA-id för källsystem</t>
-  </si>
-  <si>
-    <t>HSA-id för det system som tillgängliggör informationen.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.documentTitle</t>
-  </si>
-  <si>
-    <t>Titel (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetFunctionalStatus skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.documentTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Bedömningstidpunkt</t>
+  </si>
+  <si>
+    <t>Bedömningstidpunkt/händelsetidpunkt. Format: YYYYMMDDhhmmss.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.patientId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPersonIdTypeHealthcondDescription2
 </t>
   </si>
   <si>
-    <t>Bedömningstidpunkt</t>
-  </si>
-  <si>
-    <t>Bedömningstidpunkt/händelsetidpunkt. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.patientId</t>
-  </si>
-  <si>
     <t>Patientidentifierare</t>
   </si>
   <si>
     <t>Identifierare för patient. id = patientens identifierare (12 tecken).
-type = OID för typ av identifierare.
-Kardinalitet: Obligatorisk.</t>
+type = OID för typ av identifierare.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional</t>
@@ -433,8 +432,7 @@
     <t>Ansvarig hälso- och sjukvårdsperson</t>
   </si>
   <si>
-    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.id</t>
@@ -453,7 +451,7 @@
   </si>
   <si>
     <t>Tidpunkt då informationen registrerades. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
@@ -462,8 +460,7 @@
     <t>Författarens HSA-id</t>
   </si>
   <si>
-    <t>Författarens HSA-id.
-Kardinalitet: Valfri.</t>
+    <t>Författarens HSA-id.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
@@ -472,22 +469,20 @@
     <t>Namn</t>
   </si>
   <si>
-    <t>Namn på hälso- och sjukvårdspersonal.
-Kardinalitet: Valfri.</t>
+    <t>Namn på hälso- och sjukvårdspersonal.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeHealthcondDescription2
 </t>
   </si>
   <si>
     <t>Befattning</t>
   </si>
   <si>
-    <t>Information om personens befattning.
-Kardinalitet: Valfri.</t>
+    <t>Information om personens befattning.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
@@ -496,8 +491,7 @@
     <t>Organisationsenhet</t>
   </si>
   <si>
-    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.
-Kardinalitet: Valfri.</t>
+    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
@@ -515,8 +509,7 @@
     <t>HSA-id för organisationsenhet</t>
   </si>
   <si>
-    <t>HSA-id för organisationsenhet.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
+    <t>HSA-id för organisationsenhet.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
@@ -525,8 +518,43 @@
     <t>Namn på organisationsenhet</t>
   </si>
   <si>
-    <t>Namn på organisationsenhet.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
+    <t>Namn på organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>E-post till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Postadress till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Postadress för den organisation som författaren är uppdragstagare på.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Plats för organisationsenhet</t>
+  </si>
+  <si>
+    <t>Text som anger namnet på plats eller ort för organisationens fysiska placering.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
@@ -535,8 +563,7 @@
     <t>HSA-id för vårdenhet</t>
   </si>
   <si>
-    <t>HSA-id för vårdenhet. Se regel 1 i TKB.
-Kardinalitet: Valfri (villkorlig, se regel 1).</t>
+    <t>HSA-id för vårdenhet. Se regel 1 i TKB.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
@@ -545,8 +572,7 @@
     <t>HSA-id för vårdgivare</t>
   </si>
   <si>
-    <t>HSA-id för vårdgivaren.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för vårdgivaren.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.legalAuthenticator</t>
@@ -555,8 +581,7 @@
     <t>Signerande person</t>
   </si>
   <si>
-    <t>Information om vem som signerat informationen i dokumentet.
-Kardinalitet: Valfri.</t>
+    <t>Information om vem som signerat informationen i dokumentet.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.legalAuthenticator.id</t>
@@ -575,7 +600,7 @@
   </si>
   <si>
     <t>Signaturtidpunkt. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
@@ -584,8 +609,7 @@
     <t>HSA-id för signerande</t>
   </si>
   <si>
-    <t>HSA-id för person som signerat dokumentet.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för person som signerat dokumentet.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.legalAuthenticator.legalAuthenticatorName</t>
@@ -594,32 +618,20 @@
     <t>Namn på signerande person</t>
   </si>
   <si>
-    <t>Namn i klartext för signerande person.
-Kardinalitet: Valfri.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.legalAuthenticator.legalAuthenticatorRoleCode</t>
-  </si>
-  <si>
-    <t>Signerande persons befattning</t>
-  </si>
-  <si>
-    <t>Signerande persons befattning. Om möjligt ska kodverk användas.
-Kardinalitet: Valfri.</t>
+    <t>Namn i klartext för signerande person.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.approvedForPatient</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
     <t>Godkänd för visning till patient</t>
   </si>
   <si>
-    <t>Anger om information får delas till patient.
-Kardinalitet: Obligatorisk.</t>
+    <t>Anger om information får delas till patient.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.careContactId</t>
@@ -628,8 +640,7 @@
     <t>Vårdkontakts-id</t>
   </si>
   <si>
-    <t>Id för den vårdkontakt vid vilken bedömningen genomfördes.
-Kardinalitet: Valfri.</t>
+    <t>Id för den vårdkontakt vid vilken bedömningen genomfördes.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentHeader.nullified</t>
@@ -656,8 +667,7 @@
     <t>Bedömningens innehåll</t>
   </si>
   <si>
-    <t>FunctionalStatusAssessmentBodyType — bedömningens informationsinnehåll.
-Kardinalitet: Obligatorisk.</t>
+    <t>FunctionalStatusAssessmentBodyType — bedömningens informationsinnehåll.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.id</t>
@@ -678,7 +688,13 @@
     <t>Bedömningskategori. 'pad-pad' = PADL-bedömning, 'fun-fun' = funktionsnedsättningsbedömning.
 OBS: tjänsteproducent måste använda samma värde som categorization i engagemangsindex.
 Se AssessmentCategoryCS/AssessmentCategoryVS.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: pad-pad, fun-fun.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.assessmentCategory.value</t>
+  </si>
+  <si>
+    <t>Elementets textinnehåll</t>
   </si>
   <si>
     <t>required</t>
@@ -687,6 +703,9 @@
     <t>https://fhir.inera.se/ig/ehds-tk/ValueSet/assessmentcategory-vs</t>
   </si>
   <si>
+    <t>SEEHDSRivString.value</t>
+  </si>
+  <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.comment</t>
   </si>
   <si>
@@ -694,7 +713,6 @@
   </si>
   <si>
     <t>Kommentar till total bedömning.
-Kardinalitet: Valfri.
 Villkor (Regel): Får ENDAST anges om assessmentCategory = 'pad-pad'.</t>
   </si>
   <si>
@@ -704,8 +722,7 @@
     <t>PADL-bedömning</t>
   </si>
   <si>
-    <t>Beskriver gjorda PADL-bedömningar. Får enbart anges om assessmentCategory = 'pad-pad'.
-Kardinalitet: Valfri, lista (villkorlig på assessmentCategory).</t>
+    <t>Beskriver gjorda PADL-bedömningar. Får enbart anges om assessmentCategory = 'pad-pad'.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.padl.id</t>
@@ -724,7 +741,6 @@
   </si>
   <si>
     <t>Typ av PADL-bedömning. Kan anges med lämpligt kodsystem för PADL.
-Kardinalitet: Obligatorisk.
 Regel 2 (TKB): Då attributet avser Personlig ADL ska ENBART ett av följande värden anges per post: 'personlig hygien', 'på/avklädning', 'förflyttning', 'toalettbesök', 'födointag'.</t>
   </si>
   <si>
@@ -734,8 +750,7 @@
     <t>Textuell PADL-bedömning</t>
   </si>
   <si>
-    <t>Den textuella PADL-bedömning som gjorts i kategorin.
-Kardinalitet: Obligatorisk.</t>
+    <t>Den textuella PADL-bedömning som gjorts i kategorin.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.disability</t>
@@ -745,8 +760,7 @@
   </si>
   <si>
     <t>Beskriver gjord funktionsnedsättningsbedömning.
-Får enbart anges om assessmentCategory = 'fun-fun'.
-Kardinalitet: Valfri (villkorlig på assessmentCategory).</t>
+Får enbart anges om assessmentCategory = 'fun-fun'.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.disability.id</t>
@@ -767,8 +781,8 @@
     <t>Angivelse av kod för den funktion som bedömts nedsatt.
 Kodsystem: ICF, OID 1.2.752.116.1.1.3.
 Exempelkod: b310 = röst- och talfunktioner.
-Kardinalitet: Obligatorisk.
-CVType-begränsningar: codeSystemName och codeSystemVersion är 0..0 (får ej anges) per TKB. Om code anges ska codeSystem och displayName anges, ej originalText. Om originalText anges ska inga andra attribut anges.</t>
+CVType-begränsningar: codeSystemName och codeSystemVersion är 0..0 (får ej anges) per TKB. Om code anges ska codeSystem och displayName anges, ej originalText. Om originalText anges ska inga andra attribut anges.
+Enligt TKB i detta sammanhang: codeSystemName 0..0, codeSystemVersion 0..0.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.functionalStatusAssessment.functionalStatusAssessmentBody.disability.comment</t>
@@ -777,8 +791,7 @@
     <t>Kommentar till funktionsnedsättning</t>
   </si>
   <si>
-    <t>Kommentar med ytterligare information om funktionsnedsättningen.
-Kardinalitet: Valfri.</t>
+    <t>Kommentar med ytterligare information om funktionsnedsättningen.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.result</t>
@@ -787,8 +800,7 @@
     <t>Resultat</t>
   </si>
   <si>
-    <t>Innehåller information om begäran gick bra eller ej.
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller information om begäran gick bra eller ej.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.result.id</t>
@@ -803,15 +815,11 @@
     <t>SEEHDSLMFunctionalStatus.result.resultCode</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>Resultatkod</t>
   </si>
   <si>
     <t>Kan endast vara OK, INFO eller ERROR.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.result.errorCode</t>
@@ -821,7 +829,7 @@
   </si>
   <si>
     <t>Sätts endast om resultCode är ERROR. Tillåtna värden: INVALID_REQUEST.
-Kardinalitet: Valfri.</t>
+Tillåtna värden enligt XSD: INVALID_REQUEST.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.result.logId</t>
@@ -830,8 +838,16 @@
     <t>Log-id</t>
   </si>
   <si>
-    <t>En UUID som kan användas vid felanmälan för att spåra felet.
-Kardinalitet: Obligatorisk.</t>
+    <t>En UUID som kan användas vid felanmälan för att spåra felet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMFunctionalStatus.result.subCode</t>
+  </si>
+  <si>
+    <t>Subkod</t>
+  </si>
+  <si>
+    <t>Inga subkoder är specificerade.</t>
   </si>
   <si>
     <t>SEEHDSLMFunctionalStatus.result.message</t>
@@ -840,8 +856,7 @@
     <t>Meddelande</t>
   </si>
   <si>
-    <t>En beskrivande text som kan visas för användaren.
-Kardinalitet: Valfri.</t>
+    <t>En beskrivande text som kan visas för användaren.</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ69"/>
+  <dimension ref="A1:AJ74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="141.40234375" customWidth="true" bestFit="true"/>
@@ -1156,7 +1171,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1177,7 +1192,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="137.67578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="139.6484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2233,13 +2248,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2307,10 +2322,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2333,7 +2348,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>117</v>
@@ -2390,7 +2405,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -2433,7 +2448,7 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>120</v>
@@ -2633,13 +2648,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2707,10 +2722,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2736,10 +2751,10 @@
         <v>78</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2790,7 +2805,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -2807,10 +2822,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2907,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3009,10 +3024,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3113,10 +3128,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3142,10 +3157,10 @@
         <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3196,7 +3211,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -3213,10 +3228,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3239,13 +3254,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3296,7 +3311,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3313,10 +3328,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3339,13 +3354,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3396,7 +3411,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3413,10 +3428,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3439,13 +3454,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3496,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3513,10 +3528,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3542,10 +3557,10 @@
         <v>78</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3596,7 +3611,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3613,10 +3628,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3713,10 +3728,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3815,10 +3830,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3919,10 +3934,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3945,13 +3960,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4002,7 +4017,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -4019,10 +4034,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4045,13 +4060,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4102,7 +4117,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -4119,10 +4134,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4145,13 +4160,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4202,7 +4217,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4219,10 +4234,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4245,13 +4260,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4302,7 +4317,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4319,10 +4334,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4345,13 +4360,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4402,7 +4417,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4414,15 +4429,15 @@
         <v>72</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4445,13 +4460,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4502,7 +4517,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4519,21 +4534,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4545,17 +4560,15 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>72</v>
@@ -4592,75 +4605,71 @@
         <v>72</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>72</v>
       </c>
@@ -4708,27 +4717,27 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4736,7 +4745,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>83</v>
@@ -4751,13 +4760,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4808,10 +4817,10 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>83</v>
@@ -4820,15 +4829,15 @@
         <v>72</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4851,13 +4860,13 @@
         <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4908,7 +4917,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4925,21 +4934,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -4951,15 +4960,17 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>72</v>
@@ -4996,71 +5007,75 @@
         <v>72</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>72</v>
       </c>
@@ -5108,27 +5123,27 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5151,7 +5166,7 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>186</v>
@@ -5208,7 +5223,7 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -5251,7 +5266,7 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>189</v>
@@ -5339,7 +5354,7 @@
         <v>73</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>72</v>
@@ -5351,7 +5366,7 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>192</v>
@@ -5414,7 +5429,7 @@
         <v>73</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>72</v>
@@ -5436,10 +5451,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>72</v>
@@ -5451,13 +5466,13 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5511,10 +5526,10 @@
         <v>194</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>72</v>
@@ -5525,10 +5540,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5536,7 +5551,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>83</v>
@@ -5551,13 +5566,13 @@
         <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5608,10 +5623,10 @@
         <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>83</v>
@@ -5620,15 +5635,15 @@
         <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5639,7 +5654,7 @@
         <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5651,13 +5666,13 @@
         <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5708,13 +5723,13 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
@@ -5725,21 +5740,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -5751,17 +5766,15 @@
         <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>72</v>
@@ -5798,75 +5811,71 @@
         <v>72</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>72</v>
       </c>
@@ -5914,27 +5923,27 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5942,7 +5951,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>83</v>
@@ -5957,13 +5966,13 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5990,11 +5999,13 @@
         <v>72</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>72</v>
@@ -6012,10 +6023,10 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>83</v>
@@ -6029,21 +6040,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
@@ -6055,15 +6066,17 @@
         <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
@@ -6100,43 +6113,43 @@
         <v>72</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>208</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6149,22 +6162,26 @@
         <v>72</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>72</v>
       </c>
@@ -6212,7 +6229,7 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
@@ -6224,15 +6241,15 @@
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6240,7 +6257,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>83</v>
@@ -6255,13 +6272,13 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>215</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6312,10 +6329,10 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>83</v>
@@ -6329,21 +6346,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
@@ -6355,17 +6372,15 @@
         <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
@@ -6390,87 +6405,81 @@
         <v>72</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>222</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>72</v>
       </c>
@@ -6518,27 +6527,27 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6546,10 +6555,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>72</v>
@@ -6561,13 +6570,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6618,27 +6627,27 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6646,7 +6655,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>83</v>
@@ -6664,10 +6673,10 @@
         <v>84</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>222</v>
+        <v>86</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6718,10 +6727,10 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>220</v>
+        <v>87</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>83</v>
@@ -6735,21 +6744,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>72</v>
@@ -6761,15 +6770,17 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>72</v>
@@ -6806,71 +6817,75 @@
         <v>72</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>223</v>
+        <v>97</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>72</v>
       </c>
@@ -6918,38 +6933,38 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>72</v>
@@ -6961,17 +6976,15 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>91</v>
+        <v>231</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>72</v>
@@ -7008,75 +7021,71 @@
         <v>72</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>102</v>
+        <v>234</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>72</v>
       </c>
@@ -7124,27 +7133,27 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7152,7 +7161,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>83</v>
@@ -7167,13 +7176,13 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7224,10 +7233,10 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>83</v>
@@ -7236,15 +7245,15 @@
         <v>72</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7270,10 +7279,10 @@
         <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7324,7 +7333,7 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>232</v>
+        <v>87</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -7341,21 +7350,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>72</v>
@@ -7367,15 +7376,17 @@
         <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>72</v>
@@ -7412,71 +7423,75 @@
         <v>72</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>72</v>
       </c>
@@ -7524,38 +7539,38 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>72</v>
@@ -7567,17 +7582,15 @@
         <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>72</v>
@@ -7614,75 +7627,71 @@
         <v>72</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>72</v>
       </c>
@@ -7730,27 +7739,27 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7773,13 +7782,13 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7830,7 +7839,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -7842,15 +7851,15 @@
         <v>72</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7873,13 +7882,13 @@
         <v>72</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>242</v>
+        <v>84</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -7930,7 +7939,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>245</v>
+        <v>87</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -7947,21 +7956,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>72</v>
@@ -7973,15 +7982,17 @@
         <v>72</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>72</v>
@@ -8018,71 +8029,75 @@
         <v>72</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>252</v>
+        <v>102</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>72</v>
       </c>
@@ -8130,18 +8145,518 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
+++ b/StructureDefinition-SEEHDSLMFunctionalStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
